--- a/3k_bearing_calculator.xlsx
+++ b/3k_bearing_calculator.xlsx
@@ -749,7 +749,7 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>理论上打开 Excel 后应接近：n_rel≈1727.5 rpm，Fr_total≈101.8 N，L10h≈6.95E5 h。</t>
+          <t>理论上打开 Excel 后应接近：i≈49.29，n_rel≈1727.56 rpm，Fr_total≈101.72 N，L10h≈6.83E5 h。</t>
         </is>
       </c>
     </row>
